--- a/samples/arabic lab grades y1 s1 sample grades.xlsx
+++ b/samples/arabic lab grades y1 s1 sample grades.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">اسم الطالب</t>
   </si>
@@ -49,13 +49,16 @@
   </si>
   <si>
     <t xml:space="preserve">هبة سمير نبيل رافت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سعيد حميد سلطان عواد</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -93,6 +96,10 @@
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.500000"/>
+      <name val="Liberation Sans"/>
     </font>
   </fonts>
   <fills count="8">
@@ -202,10 +209,13 @@
     <xf fontId="4" fillId="6" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
     <xf fontId="5" fillId="7" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="5" fillId="7" borderId="3" numFmtId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="4" borderId="2" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,6 +806,14 @@
         <v>6</v>
       </c>
     </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
     <row r="24" ht="14.25"/>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
